--- a/nav_model/outputs/nav_model.xlsx
+++ b/nav_model/outputs/nav_model.xlsx
@@ -18,6 +18,8 @@
     <sheet name="Revenue streams annual" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Claims" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Asset register" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="NAV + FCF" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Equity FCF annual" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1324,7 +1326,6 @@
       <c r="G2" t="n">
         <v>2055</v>
       </c>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1428,7 +1429,6 @@
       <c r="G5" t="n">
         <v>2055</v>
       </c>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1460,7 +1460,6 @@
       <c r="G6" t="n">
         <v>2055</v>
       </c>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1528,7 +1527,6 @@
       <c r="G8" t="n">
         <v>2055</v>
       </c>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1554,7 +1552,6 @@
       <c r="E9" t="n">
         <v>1900</v>
       </c>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1586,7 +1583,6 @@
       <c r="G10" t="n">
         <v>2050</v>
       </c>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1618,7 +1614,6 @@
       <c r="G11" t="n">
         <v>2038</v>
       </c>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1650,7 +1645,6 @@
       <c r="G12" t="n">
         <v>2038</v>
       </c>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1682,7 +1676,6 @@
       <c r="G13" t="n">
         <v>2045</v>
       </c>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1714,7 +1707,6 @@
       <c r="G14" t="n">
         <v>2040</v>
       </c>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1746,7 +1738,6 @@
       <c r="G15" t="n">
         <v>2045</v>
       </c>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1778,7 +1769,6 @@
       <c r="G16" t="n">
         <v>2040</v>
       </c>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1846,7 +1836,6 @@
       <c r="G18" t="n">
         <v>2045</v>
       </c>
-      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1878,7 +1867,6 @@
       <c r="G19" t="n">
         <v>2050</v>
       </c>
-      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1982,7 +1970,6 @@
       <c r="G22" t="n">
         <v>2055</v>
       </c>
-      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2014,7 +2001,6 @@
       <c r="G23" t="n">
         <v>2045</v>
       </c>
-      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2046,7 +2032,6 @@
       <c r="G24" t="n">
         <v>2040</v>
       </c>
-      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2078,7 +2063,6 @@
       <c r="G25" t="n">
         <v>2045</v>
       </c>
-      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2110,7 +2094,6 @@
       <c r="G26" t="n">
         <v>2045</v>
       </c>
-      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2142,7 +2125,6 @@
       <c r="G27" t="n">
         <v>2040</v>
       </c>
-      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2174,7 +2156,6 @@
       <c r="G28" t="n">
         <v>2038</v>
       </c>
-      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2206,7 +2187,6 @@
       <c r="G29" t="n">
         <v>2035</v>
       </c>
-      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2238,7 +2218,6 @@
       <c r="G30" t="n">
         <v>2027</v>
       </c>
-      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2264,7 +2243,6 @@
       <c r="E31" t="n">
         <v>1274</v>
       </c>
-      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2296,7 +2274,6 @@
       <c r="G32" t="n">
         <v>2050</v>
       </c>
-      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2328,7 +2305,1708 @@
       <c r="G33" t="n">
         <v>2050</v>
       </c>
-      <c r="H33" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>scenario</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>fcf27</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>yield27</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>cum_ps</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>fwd_ps</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>total_ps</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>irr</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pv_total_ps</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>today_ps</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>naive_ps</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>7.9554</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0851</v>
+      </c>
+      <c r="E2" t="n">
+        <v>72.6011</v>
+      </c>
+      <c r="F2" t="n">
+        <v>55.8617</v>
+      </c>
+      <c r="G2" t="n">
+        <v>128.4628</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.1558</v>
+      </c>
+      <c r="I2" t="n">
+        <v>100.4862</v>
+      </c>
+      <c r="J2" t="n">
+        <v>93.6392</v>
+      </c>
+      <c r="K2" t="n">
+        <v>166.2403</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>8.0281</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0859</v>
+      </c>
+      <c r="E3" t="n">
+        <v>87.5294</v>
+      </c>
+      <c r="F3" t="n">
+        <v>174.9623</v>
+      </c>
+      <c r="G3" t="n">
+        <v>262.4916</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.0013</v>
+      </c>
+      <c r="I3" t="n">
+        <v>194.2765</v>
+      </c>
+      <c r="J3" t="n">
+        <v>189.6628</v>
+      </c>
+      <c r="K3" t="n">
+        <v>277.1922</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>8.1008</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.0866</v>
+      </c>
+      <c r="E4" t="n">
+        <v>103.0812</v>
+      </c>
+      <c r="F4" t="n">
+        <v>295.4722</v>
+      </c>
+      <c r="G4" t="n">
+        <v>398.5533</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.1018</v>
+      </c>
+      <c r="I4" t="n">
+        <v>289.5044</v>
+      </c>
+      <c r="J4" t="n">
+        <v>287.0323</v>
+      </c>
+      <c r="K4" t="n">
+        <v>390.1134</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>8.189299999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0876</v>
+      </c>
+      <c r="E5" t="n">
+        <v>126.1365</v>
+      </c>
+      <c r="F5" t="n">
+        <v>474.4976</v>
+      </c>
+      <c r="G5" t="n">
+        <v>600.6342</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2135</v>
+      </c>
+      <c r="I5" t="n">
+        <v>430.9156</v>
+      </c>
+      <c r="J5" t="n">
+        <v>431.5404</v>
+      </c>
+      <c r="K5" t="n">
+        <v>557.677</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5.8357</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="E6" t="n">
+        <v>48.1748</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="G6" t="n">
+        <v>50.3668</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.2122</v>
+      </c>
+      <c r="I6" t="n">
+        <v>42.7681</v>
+      </c>
+      <c r="J6" t="n">
+        <v>27.0779</v>
+      </c>
+      <c r="K6" t="n">
+        <v>75.25279999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5.9059</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1248</v>
+      </c>
+      <c r="E7" t="n">
+        <v>59.1173</v>
+      </c>
+      <c r="F7" t="n">
+        <v>70.46210000000001</v>
+      </c>
+      <c r="G7" t="n">
+        <v>129.5794</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="I7" t="n">
+        <v>98.3381</v>
+      </c>
+      <c r="J7" t="n">
+        <v>82.06619999999999</v>
+      </c>
+      <c r="K7" t="n">
+        <v>141.1835</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>5.976</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1263</v>
+      </c>
+      <c r="E8" t="n">
+        <v>71.1301</v>
+      </c>
+      <c r="F8" t="n">
+        <v>142.4178</v>
+      </c>
+      <c r="G8" t="n">
+        <v>213.5479</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.1068</v>
+      </c>
+      <c r="I8" t="n">
+        <v>157.2585</v>
+      </c>
+      <c r="J8" t="n">
+        <v>140.311</v>
+      </c>
+      <c r="K8" t="n">
+        <v>211.4411</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>6.0615</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1281</v>
+      </c>
+      <c r="E9" t="n">
+        <v>89.4744</v>
+      </c>
+      <c r="F9" t="n">
+        <v>252.5365</v>
+      </c>
+      <c r="G9" t="n">
+        <v>342.0109</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.2365</v>
+      </c>
+      <c r="I9" t="n">
+        <v>247.3764</v>
+      </c>
+      <c r="J9" t="n">
+        <v>229.3551</v>
+      </c>
+      <c r="K9" t="n">
+        <v>318.8295</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>scenario</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>asset_margin</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>tax</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>pref</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>fcf</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2027</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.299</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10.112</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.989</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>7.955</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2028</v>
+      </c>
+      <c r="D3" t="n">
+        <v>22.286</v>
+      </c>
+      <c r="E3" t="n">
+        <v>11.095</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.188</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>8.750999999999999</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2029</v>
+      </c>
+      <c r="D4" t="n">
+        <v>18.734</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7.246</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.061</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.415</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5.686</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D5" t="n">
+        <v>15.936</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4.271</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.331</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2027</v>
+      </c>
+      <c r="D6" t="n">
+        <v>21.384</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10.203</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.007</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8.028</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2028</v>
+      </c>
+      <c r="D7" t="n">
+        <v>22.372</v>
+      </c>
+      <c r="E7" t="n">
+        <v>11.188</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.206</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>8.824999999999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2029</v>
+      </c>
+      <c r="D8" t="n">
+        <v>21.049</v>
+      </c>
+      <c r="E8" t="n">
+        <v>9.541</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.061</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.879</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7.516</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D9" t="n">
+        <v>20.214</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8.436999999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.661</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6.643</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2027</v>
+      </c>
+      <c r="D10" t="n">
+        <v>21.468</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10.294</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.025</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8.101000000000001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2028</v>
+      </c>
+      <c r="D11" t="n">
+        <v>22.458</v>
+      </c>
+      <c r="E11" t="n">
+        <v>11.281</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8.898999999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2029</v>
+      </c>
+      <c r="D12" t="n">
+        <v>23.393</v>
+      </c>
+      <c r="E12" t="n">
+        <v>11.891</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.061</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.349</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>9.396000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D13" t="n">
+        <v>24.562</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12.792</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.532</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>10.126</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2027</v>
+      </c>
+      <c r="D14" t="n">
+        <v>21.569</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10.405</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>8.189</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2028</v>
+      </c>
+      <c r="D15" t="n">
+        <v>22.562</v>
+      </c>
+      <c r="E15" t="n">
+        <v>11.393</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>8.989000000000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2029</v>
+      </c>
+      <c r="D16" t="n">
+        <v>26.861</v>
+      </c>
+      <c r="E16" t="n">
+        <v>15.369</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.061</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.045</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>12.179</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D17" t="n">
+        <v>31.062</v>
+      </c>
+      <c r="E17" t="n">
+        <v>19.301</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.834</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>15.334</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2027</v>
+      </c>
+      <c r="D18" t="n">
+        <v>16.917</v>
+      </c>
+      <c r="E18" t="n">
+        <v>7.677</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.492</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5.836</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2028</v>
+      </c>
+      <c r="D19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>6.901</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.522</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.355</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5.233</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2029</v>
+      </c>
+      <c r="D20" t="n">
+        <v>13.301</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.553</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.312</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D21" t="n">
+        <v>11.775</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.851</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.047</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2027</v>
+      </c>
+      <c r="D22" t="n">
+        <v>16.998</v>
+      </c>
+      <c r="E22" t="n">
+        <v>7.765</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.492</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.523</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5.906</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2028</v>
+      </c>
+      <c r="D23" t="n">
+        <v>15.583</v>
+      </c>
+      <c r="E23" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.522</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.373</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5.304</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2029</v>
+      </c>
+      <c r="D24" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6.068</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.553</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.193</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.585</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D25" t="n">
+        <v>14.829</v>
+      </c>
+      <c r="E25" t="n">
+        <v>5.768</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.137</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.364</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2027</v>
+      </c>
+      <c r="D26" t="n">
+        <v>17.079</v>
+      </c>
+      <c r="E26" t="n">
+        <v>7.853</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.492</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="K26" t="n">
+        <v>5.976</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2028</v>
+      </c>
+      <c r="D27" t="n">
+        <v>15.666</v>
+      </c>
+      <c r="E27" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.522</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5.376</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2029</v>
+      </c>
+      <c r="D28" t="n">
+        <v>16.658</v>
+      </c>
+      <c r="E28" t="n">
+        <v>7.793</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.553</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.538</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5.965</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D29" t="n">
+        <v>18.041</v>
+      </c>
+      <c r="E29" t="n">
+        <v>8.986000000000001</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.781</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="K29" t="n">
+        <v>6.939</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2027</v>
+      </c>
+      <c r="D30" t="n">
+        <v>17.176</v>
+      </c>
+      <c r="E30" t="n">
+        <v>7.959</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.492</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.562</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="K30" t="n">
+        <v>6.061</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2028</v>
+      </c>
+      <c r="D31" t="n">
+        <v>15.765</v>
+      </c>
+      <c r="E31" t="n">
+        <v>7.189</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.522</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.412</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="K31" t="n">
+        <v>5.463</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2029</v>
+      </c>
+      <c r="D32" t="n">
+        <v>19.284</v>
+      </c>
+      <c r="E32" t="n">
+        <v>10.429</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.553</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.065</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="K32" t="n">
+        <v>8.074</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D33" t="n">
+        <v>22.998</v>
+      </c>
+      <c r="E33" t="n">
+        <v>13.954</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.774</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="K33" t="n">
+        <v>10.912</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/nav_model/outputs/nav_model.xlsx
+++ b/nav_model/outputs/nav_model.xlsx
@@ -20,6 +20,8 @@
     <sheet name="Asset register" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="NAV + FCF" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Equity FCF annual" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Replacement cost" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Replacement + FCF" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4013,6 +4015,5541 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I65"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>basis</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>mw</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>rc_kw</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>frac</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>rcn_bn</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>drc_bn</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Nuclear - PJM East (Limerick, Peach Bottom 50%, Calvert Cliffs, Salem 42.6%)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>nuclear</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>6430</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12100</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H2" t="n">
+        <v>77.803</v>
+      </c>
+      <c r="I2" t="n">
+        <v>29.555</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Nuclear - PJM ComEd (Byron, Braidwood, LaSalle, Dresden, Quad Cities 75%)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>nuclear</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>10300</v>
+      </c>
+      <c r="F3" t="n">
+        <v>12100</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="H3" t="n">
+        <v>124.63</v>
+      </c>
+      <c r="I3" t="n">
+        <v>47.966</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Nuclear - Clinton (MISO) - Meta 20-yr PPA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>nuclear</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1080</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12100</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="H4" t="n">
+        <v>13.068</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5.54</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Nuclear - New York (Nine Mile Pt, Ginna, FitzPatrick)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>nuclear</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>12100</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="H5" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>12.948</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Nuclear - South Texas Project 44% (ERCOT)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>nuclear</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1165</v>
+      </c>
+      <c r="F6" t="n">
+        <v>12100</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H6" t="n">
+        <v>14.097</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6.064</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Nuclear - Crane restart (TMI-1) - Microsoft 20-yr PPA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>nuclear</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>835</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12100</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="H7" t="n">
+        <v>10.104</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.524</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Hydro - Conowingo + Muddy Run pumped storage (PJM)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>hydro</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1642</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5.747</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.873</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Wind &amp; solar (legacy CEG, ~1.9 GW)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>renewable</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1900</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.064</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Gas - ERCOT CCGT (Colorado Bend II, Wolf Hollow II, etc.)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ccgt</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.405</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.855</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Gas/oil - ERCOT peakers &amp; steam (legacy CEG)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>peaker</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1277</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1970</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.629</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Gas/oil - PJM/NE/other peakers &amp; oil (legacy CEG)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>peaker</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2582</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1970</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5.087</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.416</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Calpine - ERCOT CCGT (Deer Park, Freestone, Channel, Baytown, etc.)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ccgt</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="H13" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="I13" t="n">
+        <v>7.197</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Calpine - ERCOT peakers/cogen</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>peaker</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>400</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1970</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.274</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Calpine - West CCGT (CAISO)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ccgt</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="H15" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5.26</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Calpine - West peakers</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>peaker</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>800</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1970</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.576</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.576</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Calpine - The Geysers geothermal</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>geothermal</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>750</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.125</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.699</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Calpine - East CCGT (NE/NY/PJM residual/SE)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ccgt</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2900</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="H18" t="n">
+        <v>6.815</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.051</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>RISEC (609 MW CCGT, ISO-NE) - pending, $715mm</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ccgt</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>609</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.431</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.708</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Nuclear - PJM East (Limerick, Peach Bottom 50%, Calvert Cliffs, Salem 42.6%)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>nuclear</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6430</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2862.179</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H20" t="n">
+        <v>18.404</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6.991</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Nuclear - PJM ComEd (Byron, Braidwood, LaSalle, Dresden, Quad Cities 75%)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>nuclear</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>10300</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2862.179</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="H21" t="n">
+        <v>29.48</v>
+      </c>
+      <c r="I21" t="n">
+        <v>11.346</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Nuclear - Clinton (MISO) - Meta 20-yr PPA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>nuclear</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1080</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2862.179</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.091</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Nuclear - New York (Nine Mile Pt, Ginna, FitzPatrick)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>nuclear</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2862.179</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="H23" t="n">
+        <v>8.587</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.063</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Nuclear - South Texas Project 44% (ERCOT)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>nuclear</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1165</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2862.179</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.334</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.434</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Nuclear - Crane restart (TMI-1) - Microsoft 20-yr PPA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>nuclear</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>835</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2862.179</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.834</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Hydro - Conowingo + Muddy Run pumped storage (PJM)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>hydro</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1642</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>5.747</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.873</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Wind &amp; solar (legacy CEG, ~1.9 GW)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>renewable</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1900</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.064</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Gas - ERCOT CCGT (Colorado Bend II, Wolf Hollow II, etc.)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ccgt</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="H28" t="n">
+        <v>5.405</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3.855</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Gas/oil - ERCOT peakers &amp; steam (legacy CEG)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>peaker</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1277</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1970</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.629</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Gas/oil - PJM/NE/other peakers &amp; oil (legacy CEG)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>peaker</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2582</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1970</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="H30" t="n">
+        <v>5.087</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.416</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Calpine - ERCOT CCGT (Deer Park, Freestone, Channel, Baytown, etc.)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ccgt</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="H31" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="I31" t="n">
+        <v>7.197</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Calpine - ERCOT peakers/cogen</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>peaker</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>400</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1970</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.274</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Calpine - West CCGT (CAISO)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ccgt</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="H33" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="I33" t="n">
+        <v>5.26</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Calpine - West peakers</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>peaker</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>800</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1970</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.576</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.576</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Calpine - The Geysers geothermal</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>geothermal</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>750</v>
+      </c>
+      <c r="F35" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4.125</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.699</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Calpine - East CCGT (NE/NY/PJM residual/SE)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ccgt</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2900</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="H36" t="n">
+        <v>6.815</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3.051</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>RISEC (609 MW CCGT, ISO-NE) - pending, $715mm</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ccgt</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>609</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.431</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.708</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Nuclear - Comanche Peak (ERCOT) - 1,200 MW 20-yr PPA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>nuclear</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F38" t="n">
+        <v>12100</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="H38" t="n">
+        <v>29.04</v>
+      </c>
+      <c r="I38" t="n">
+        <v>12.561</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Nuclear - Perry + Davis-Besse (PJM ATSI) - Meta 20-yr PPAs</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>nuclear</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2176</v>
+      </c>
+      <c r="F39" t="n">
+        <v>12100</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="H39" t="n">
+        <v>26.33</v>
+      </c>
+      <c r="I39" t="n">
+        <v>10.55</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Nuclear - Beaver Valley (PJM)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>nuclear</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F40" t="n">
+        <v>12100</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H40" t="n">
+        <v>22.651</v>
+      </c>
+      <c r="I40" t="n">
+        <v>8.834</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Gas - ERCOT CCGT</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ccgt</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>9500</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="H41" t="n">
+        <v>22.325</v>
+      </c>
+      <c r="I41" t="n">
+        <v>9.994</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Gas - ERCOT peakers</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>peaker</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1970</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="H42" t="n">
+        <v>4.531</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.575</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Gas - PJM CCGT (incl. Lotus)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ccgt</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>8500</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="H43" t="n">
+        <v>19.975</v>
+      </c>
+      <c r="I43" t="n">
+        <v>9.154999999999999</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Gas - NY/NE CCGT</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ccgt</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>3167</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="H44" t="n">
+        <v>7.442</v>
+      </c>
+      <c r="I44" t="n">
+        <v>3.256</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Gas - West CCGT (CAISO)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ccgt</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.859</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Gas/oil - East peakers</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>peaker</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2709</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1970</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="H46" t="n">
+        <v>5.337</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.595</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Coal - ERCOT (Martin Lake, Oak Grove, Coleto Creek)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>coal</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="H47" t="n">
+        <v>10.575</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1.747</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Coal - IL/OH (Baldwin, Kincaid, Newton, Miami Fort) - retiring ~2027</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>coal</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>4243</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="H48" t="n">
+        <v>9.971</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.235</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Solar &amp; batteries (Vistra Zero)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>renewable</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1274</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2.038</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1.121</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Cogentrix (pending) - modern CCGT, PJM</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ccgt</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>3850</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="H50" t="n">
+        <v>9.047000000000001</v>
+      </c>
+      <c r="I50" t="n">
+        <v>5.626</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>like-for-like nuclear</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Cogentrix (pending) - modern CCGT, NE</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ccgt</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="H51" t="n">
+        <v>3.877</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2.411</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Nuclear - Comanche Peak (ERCOT) - 1,200 MW 20-yr PPA</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>nuclear</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2862.179</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="H52" t="n">
+        <v>6.869</v>
+      </c>
+      <c r="I52" t="n">
+        <v>2.971</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Nuclear - Perry + Davis-Besse (PJM ATSI) - Meta 20-yr PPAs</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>nuclear</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>2176</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2862.179</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="H53" t="n">
+        <v>6.228</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2.496</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Nuclear - Beaver Valley (PJM)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>nuclear</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2862.179</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H54" t="n">
+        <v>5.358</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Gas - ERCOT CCGT</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ccgt</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>9500</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="H55" t="n">
+        <v>22.325</v>
+      </c>
+      <c r="I55" t="n">
+        <v>9.994</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Gas - ERCOT peakers</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>peaker</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1970</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="H56" t="n">
+        <v>4.531</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1.575</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Gas - PJM CCGT (incl. Lotus)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ccgt</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>8500</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="H57" t="n">
+        <v>19.975</v>
+      </c>
+      <c r="I57" t="n">
+        <v>9.154999999999999</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Gas - NY/NE CCGT</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ccgt</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>3167</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="H58" t="n">
+        <v>7.442</v>
+      </c>
+      <c r="I58" t="n">
+        <v>3.256</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Gas - West CCGT (CAISO)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ccgt</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="H59" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.859</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Gas/oil - East peakers</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>peaker</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>2709</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1970</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="H60" t="n">
+        <v>5.337</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1.595</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Coal - ERCOT (Martin Lake, Oak Grove, Coleto Creek)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>coal</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="H61" t="n">
+        <v>10.575</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1.747</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Coal - IL/OH (Baldwin, Kincaid, Newton, Miami Fort) - retiring ~2027</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>coal</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>4243</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="H62" t="n">
+        <v>9.971</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.235</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Solar &amp; batteries (Vistra Zero)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>renewable</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1274</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2.038</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1.121</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Cogentrix (pending) - modern CCGT, PJM</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ccgt</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>3850</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="H64" t="n">
+        <v>9.047000000000001</v>
+      </c>
+      <c r="I64" t="n">
+        <v>5.626</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>functional nuclear (CCGT)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Cogentrix (pending) - modern CCGT, NE</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ccgt</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F65" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="H65" t="n">
+        <v>3.877</v>
+      </c>
+      <c r="I65" t="n">
+        <v>2.411</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J81"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>basis</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>horizon_yrs</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>scenario</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>drc_bn</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pv_fcf_bn</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>cum_fcf_bn</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>value_ps</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>price_vs_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>134.2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>336.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-0.216</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>134.2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>336.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-0.216</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>134.2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>336.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0.216</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>134.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>336.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0.216</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>134.2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="G6" t="n">
+        <v>22.39</v>
+      </c>
+      <c r="H6" t="n">
+        <v>391.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0.326</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>134.2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="G7" t="n">
+        <v>24.37</v>
+      </c>
+      <c r="H7" t="n">
+        <v>395.9</v>
+      </c>
+      <c r="I7" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.333</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>134.2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>22.66</v>
+      </c>
+      <c r="G8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>400.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.341</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>134.2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>25.02</v>
+      </c>
+      <c r="G9" t="n">
+        <v>29.36</v>
+      </c>
+      <c r="H9" t="n">
+        <v>407.2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.352</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>134.2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>29.06</v>
+      </c>
+      <c r="H10" t="n">
+        <v>404.6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0.348</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>134.2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>30.31</v>
+      </c>
+      <c r="G11" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="H11" t="n">
+        <v>422.1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0.375</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>134.2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>36.81</v>
+      </c>
+      <c r="G12" t="n">
+        <v>46.79</v>
+      </c>
+      <c r="H12" t="n">
+        <v>440.4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0.401</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>134.2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="G13" t="n">
+        <v>60.27</v>
+      </c>
+      <c r="H13" t="n">
+        <v>467.7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0.436</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>134.2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>27.94</v>
+      </c>
+      <c r="G14" t="n">
+        <v>35.64</v>
+      </c>
+      <c r="H14" t="n">
+        <v>415.4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.365</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>134.2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>38.29</v>
+      </c>
+      <c r="G15" t="n">
+        <v>51.38</v>
+      </c>
+      <c r="H15" t="n">
+        <v>444.6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0.406</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>134.2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>49.06</v>
+      </c>
+      <c r="G16" t="n">
+        <v>67.76000000000001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>475</v>
+      </c>
+      <c r="I16" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0.444</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>7</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>134.2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="G17" t="n">
+        <v>92.19</v>
+      </c>
+      <c r="H17" t="n">
+        <v>520.3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.493</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>134.2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="G18" t="n">
+        <v>45.28</v>
+      </c>
+      <c r="H18" t="n">
+        <v>428.3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.384</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>134.2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>48.21</v>
+      </c>
+      <c r="G19" t="n">
+        <v>72.43000000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>472.6</v>
+      </c>
+      <c r="I19" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-0.442</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>134.2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="G20" t="n">
+        <v>100.44</v>
+      </c>
+      <c r="H20" t="n">
+        <v>518.5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-0.491</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>134.2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>88.67</v>
+      </c>
+      <c r="G21" t="n">
+        <v>142.23</v>
+      </c>
+      <c r="H21" t="n">
+        <v>586.8</v>
+      </c>
+      <c r="I21" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>109</v>
+      </c>
+      <c r="I22" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.421</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>109</v>
+      </c>
+      <c r="I23" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.421</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>109</v>
+      </c>
+      <c r="I24" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.421</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>109</v>
+      </c>
+      <c r="I25" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.421</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="F26" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="G26" t="n">
+        <v>22.39</v>
+      </c>
+      <c r="H26" t="n">
+        <v>164</v>
+      </c>
+      <c r="I26" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="F27" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="G27" t="n">
+        <v>24.37</v>
+      </c>
+      <c r="H27" t="n">
+        <v>168.4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="F28" t="n">
+        <v>22.66</v>
+      </c>
+      <c r="G28" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="H28" t="n">
+        <v>173</v>
+      </c>
+      <c r="I28" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.526</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="F29" t="n">
+        <v>25.02</v>
+      </c>
+      <c r="G29" t="n">
+        <v>29.36</v>
+      </c>
+      <c r="H29" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="I29" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.469</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="F30" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>29.06</v>
+      </c>
+      <c r="H30" t="n">
+        <v>177</v>
+      </c>
+      <c r="I30" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.491</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="F31" t="n">
+        <v>30.31</v>
+      </c>
+      <c r="G31" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="H31" t="n">
+        <v>194.6</v>
+      </c>
+      <c r="I31" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.356</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="F32" t="n">
+        <v>36.81</v>
+      </c>
+      <c r="G32" t="n">
+        <v>46.79</v>
+      </c>
+      <c r="H32" t="n">
+        <v>212.9</v>
+      </c>
+      <c r="I32" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="F33" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="G33" t="n">
+        <v>60.27</v>
+      </c>
+      <c r="H33" t="n">
+        <v>240.1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.099</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>7</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="F34" t="n">
+        <v>27.94</v>
+      </c>
+      <c r="G34" t="n">
+        <v>35.64</v>
+      </c>
+      <c r="H34" t="n">
+        <v>187.9</v>
+      </c>
+      <c r="I34" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.405</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>7</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="F35" t="n">
+        <v>38.29</v>
+      </c>
+      <c r="G35" t="n">
+        <v>51.38</v>
+      </c>
+      <c r="H35" t="n">
+        <v>217.1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.216</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>7</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="F36" t="n">
+        <v>49.06</v>
+      </c>
+      <c r="G36" t="n">
+        <v>67.76000000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>247.5</v>
+      </c>
+      <c r="I36" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.067</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>7</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="F37" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="G37" t="n">
+        <v>92.19</v>
+      </c>
+      <c r="H37" t="n">
+        <v>292.7</v>
+      </c>
+      <c r="I37" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-0.098</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>10</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="F38" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="G38" t="n">
+        <v>45.28</v>
+      </c>
+      <c r="H38" t="n">
+        <v>200.7</v>
+      </c>
+      <c r="I38" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.315</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>10</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="F39" t="n">
+        <v>48.21</v>
+      </c>
+      <c r="G39" t="n">
+        <v>72.43000000000001</v>
+      </c>
+      <c r="H39" t="n">
+        <v>245.1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.077</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>10</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="F40" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="G40" t="n">
+        <v>100.44</v>
+      </c>
+      <c r="H40" t="n">
+        <v>290.9</v>
+      </c>
+      <c r="I40" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-0.093</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>10</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="F41" t="n">
+        <v>88.67</v>
+      </c>
+      <c r="G41" t="n">
+        <v>142.23</v>
+      </c>
+      <c r="H41" t="n">
+        <v>359.3</v>
+      </c>
+      <c r="I41" t="n">
+        <v>263.93</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-0.265</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>125.9</v>
+      </c>
+      <c r="I42" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.102</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>125.9</v>
+      </c>
+      <c r="I43" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.102</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>125.9</v>
+      </c>
+      <c r="I44" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.102</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>125.9</v>
+      </c>
+      <c r="I45" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.102</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="F46" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="G46" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="H46" t="n">
+        <v>162.8</v>
+      </c>
+      <c r="I46" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J46" t="n">
+        <v>-0.148</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="F47" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="G47" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H47" t="n">
+        <v>166.1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J47" t="n">
+        <v>-0.165</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="F48" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="G48" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="H48" t="n">
+        <v>169.7</v>
+      </c>
+      <c r="I48" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J48" t="n">
+        <v>-0.182</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="F49" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="G49" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H49" t="n">
+        <v>175</v>
+      </c>
+      <c r="I49" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J49" t="n">
+        <v>-0.207</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="F50" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="G50" t="n">
+        <v>18.54</v>
+      </c>
+      <c r="H50" t="n">
+        <v>171.3</v>
+      </c>
+      <c r="I50" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J50" t="n">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>5</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="F51" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="G51" t="n">
+        <v>24.63</v>
+      </c>
+      <c r="H51" t="n">
+        <v>184.1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J51" t="n">
+        <v>-0.246</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>5</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="F52" t="n">
+        <v>24.66</v>
+      </c>
+      <c r="G52" t="n">
+        <v>31.34</v>
+      </c>
+      <c r="H52" t="n">
+        <v>198.2</v>
+      </c>
+      <c r="I52" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J52" t="n">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>5</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="F53" t="n">
+        <v>32.03</v>
+      </c>
+      <c r="G53" t="n">
+        <v>41.62</v>
+      </c>
+      <c r="H53" t="n">
+        <v>219.8</v>
+      </c>
+      <c r="I53" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J53" t="n">
+        <v>-0.369</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>7</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="F54" t="n">
+        <v>18</v>
+      </c>
+      <c r="G54" t="n">
+        <v>22.88</v>
+      </c>
+      <c r="H54" t="n">
+        <v>178.7</v>
+      </c>
+      <c r="I54" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J54" t="n">
+        <v>-0.223</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>7</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="F55" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="G55" t="n">
+        <v>33.88</v>
+      </c>
+      <c r="H55" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="I55" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J55" t="n">
+        <v>-0.306</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>7</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="F56" t="n">
+        <v>33.17</v>
+      </c>
+      <c r="G56" t="n">
+        <v>45.92</v>
+      </c>
+      <c r="H56" t="n">
+        <v>223.2</v>
+      </c>
+      <c r="I56" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J56" t="n">
+        <v>-0.378</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>7</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="F57" t="n">
+        <v>45.34</v>
+      </c>
+      <c r="G57" t="n">
+        <v>64.42</v>
+      </c>
+      <c r="H57" t="n">
+        <v>258.9</v>
+      </c>
+      <c r="I57" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J57" t="n">
+        <v>-0.464</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>10</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="F58" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="G58" t="n">
+        <v>29.44</v>
+      </c>
+      <c r="H58" t="n">
+        <v>187.8</v>
+      </c>
+      <c r="I58" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J58" t="n">
+        <v>-0.261</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>10</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="F59" t="n">
+        <v>31.97</v>
+      </c>
+      <c r="G59" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="H59" t="n">
+        <v>219.7</v>
+      </c>
+      <c r="I59" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J59" t="n">
+        <v>-0.368</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>10</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="F60" t="n">
+        <v>43.76</v>
+      </c>
+      <c r="G60" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="H60" t="n">
+        <v>254.2</v>
+      </c>
+      <c r="I60" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J60" t="n">
+        <v>-0.454</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>10</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="F61" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="G61" t="n">
+        <v>99.42</v>
+      </c>
+      <c r="H61" t="n">
+        <v>307.3</v>
+      </c>
+      <c r="I61" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J61" t="n">
+        <v>-0.548</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="I62" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1.552</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="I63" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1.552</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="I64" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.552</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="I65" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1.552</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>3</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="F66" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="G66" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="H66" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="I66" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>3</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="F67" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="G67" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H67" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="I67" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.467</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>3</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="F68" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="G68" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="H68" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="I68" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.413</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>3</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="F69" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="G69" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H69" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="I69" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.341</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>5</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="F70" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="G70" t="n">
+        <v>18.54</v>
+      </c>
+      <c r="H70" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="I70" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.391</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>5</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="F71" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="G71" t="n">
+        <v>24.63</v>
+      </c>
+      <c r="H71" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="I71" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.233</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>5</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="F72" t="n">
+        <v>24.66</v>
+      </c>
+      <c r="G72" t="n">
+        <v>31.34</v>
+      </c>
+      <c r="H72" t="n">
+        <v>126.7</v>
+      </c>
+      <c r="I72" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.095</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>5</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="F73" t="n">
+        <v>32.03</v>
+      </c>
+      <c r="G73" t="n">
+        <v>41.62</v>
+      </c>
+      <c r="H73" t="n">
+        <v>148.3</v>
+      </c>
+      <c r="I73" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J73" t="n">
+        <v>-0.064</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>7</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="F74" t="n">
+        <v>18</v>
+      </c>
+      <c r="G74" t="n">
+        <v>22.88</v>
+      </c>
+      <c r="H74" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="I74" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.295</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>7</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="F75" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="G75" t="n">
+        <v>33.88</v>
+      </c>
+      <c r="H75" t="n">
+        <v>128.4</v>
+      </c>
+      <c r="I75" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.081</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>7</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="F76" t="n">
+        <v>33.17</v>
+      </c>
+      <c r="G76" t="n">
+        <v>45.92</v>
+      </c>
+      <c r="H76" t="n">
+        <v>151.7</v>
+      </c>
+      <c r="I76" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J76" t="n">
+        <v>-0.08500000000000001</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>7</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="F77" t="n">
+        <v>45.34</v>
+      </c>
+      <c r="G77" t="n">
+        <v>64.42</v>
+      </c>
+      <c r="H77" t="n">
+        <v>187.3</v>
+      </c>
+      <c r="I77" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J77" t="n">
+        <v>-0.259</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>10</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="F78" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="G78" t="n">
+        <v>29.44</v>
+      </c>
+      <c r="H78" t="n">
+        <v>116.2</v>
+      </c>
+      <c r="I78" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.194</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>10</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="F79" t="n">
+        <v>31.97</v>
+      </c>
+      <c r="G79" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="H79" t="n">
+        <v>148.1</v>
+      </c>
+      <c r="I79" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J79" t="n">
+        <v>-0.063</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>10</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="F80" t="n">
+        <v>43.76</v>
+      </c>
+      <c r="G80" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="H80" t="n">
+        <v>182.7</v>
+      </c>
+      <c r="I80" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J80" t="n">
+        <v>-0.241</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>10</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="F81" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="G81" t="n">
+        <v>99.42</v>
+      </c>
+      <c r="H81" t="n">
+        <v>235.8</v>
+      </c>
+      <c r="I81" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="J81" t="n">
+        <v>-0.411</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
